--- a/assets/data/excel/dungeon.xlsx
+++ b/assets/data/excel/dungeon.xlsx
@@ -453,72 +453,119 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
-      <c r="B1" s="1" t="n"/>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>floor</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>enemyDensity</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>chestProbability</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>shopProbability</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>enemyLevels</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>goldMultiplier</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>expMultiplier</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>float</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>敌人密度</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>宝箱概率</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>商店概率</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>敌人等级范围</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>金币倍率</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>经验倍率</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -546,48 +593,36 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>floor</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>enemyDensity</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>chestProbability</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>shopProbability</t>
-        </is>
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.15</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>enemyLevels</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>goldMultiplier</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>expMultiplier</t>
-        </is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="C6" t="n">
         <v>0.2</v>
@@ -597,22 +632,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B7" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="C7" t="n">
         <v>0.2</v>
@@ -622,22 +657,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B8" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C8" t="n">
         <v>0.2</v>
@@ -647,22 +682,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B9" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="C9" t="n">
         <v>0.2</v>
@@ -672,22 +707,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B10" t="n">
-        <v>0.65</v>
+        <v>0.8</v>
       </c>
       <c r="C10" t="n">
         <v>0.2</v>
@@ -697,22 +732,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>4-5</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="G10" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B11" t="n">
-        <v>0.6</v>
+        <v>0.85</v>
       </c>
       <c r="C11" t="n">
         <v>0.2</v>
@@ -722,22 +757,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>4-5</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="G11" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B12" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="C12" t="n">
         <v>0.2</v>
@@ -747,47 +782,47 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>5-6</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="G12" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B13" t="n">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="D13" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>6-7</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B14" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
         <v>0.2</v>
@@ -797,22 +832,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>7-8</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="G14" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
         <v>0.2</v>
@@ -822,22 +857,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>7-8</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="G15" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
         <v>0.2</v>
@@ -847,22 +882,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4-5</t>
+          <t>8-9</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="G16" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B17" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
         <v>0.2</v>
@@ -872,22 +907,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>8-9</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B18" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
         <v>0.2</v>
@@ -897,22 +932,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4-5</t>
+          <t>9-10</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="G18" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B19" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>0.2</v>
@@ -922,22 +957,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4-5</t>
+          <t>9-10</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="G19" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B20" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
         <v>0.2</v>
@@ -947,22 +982,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>10-11</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="G20" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B21" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
         <v>0.2</v>
@@ -972,69 +1007,69 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4-5</t>
+          <t>10-11</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="G21" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>6-7</t>
+          <t>11-12</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B23" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="D23" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>12-13</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B24" t="n">
         <v>1</v>
@@ -1047,509 +1082,739 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>7-8</t>
+          <t>12-13</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="G24" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>6-7</t>
+          <t>12-14</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="D26" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>7-8</t>
+          <t>13-14</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="G26" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="C27" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="D27" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>7-8</t>
+          <t>13-15</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="G27" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="C28" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="D28" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>8-9</t>
+          <t>14-15</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="G28" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="C29" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="D29" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>7-8</t>
+          <t>14-16</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="G29" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="C30" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="D30" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>8-9</t>
+          <t>15-16</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="G30" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="D31" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>8-9</t>
+          <t>15-17</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="G31" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="C32" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="D32" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>9-10</t>
+          <t>16-17</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="G32" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="D33" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>8-9</t>
+          <t>17-18</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="G33" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="C34" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="D34" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>9-10</t>
+          <t>17-18</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="G34" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>1.24</v>
       </c>
       <c r="C35" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="D35" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>9-10</t>
+          <t>18-19</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="G35" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>1.28</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="D36" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>10-11</t>
+          <t>18-19</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="G36" t="n">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="B37" t="n">
-        <v>1</v>
+        <v>1.32</v>
       </c>
       <c r="C37" t="n">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="D37" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>9-10</t>
+          <t>19-20</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="G37" t="n">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="D38" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>10-11</t>
+          <t>19-20</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="G38" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="D39" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>10-11</t>
+          <t>20-21</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="G39" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>1.44</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2</v>
+        <v>0.28</v>
       </c>
       <c r="D40" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>11-12</t>
+          <t>20-22</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.9</v>
+        <v>4.9</v>
       </c>
       <c r="G40" t="n">
-        <v>2.9</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>1.48</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2</v>
+        <v>0.28</v>
       </c>
       <c r="D41" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>10-11</t>
+          <t>21-22</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="G41" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="C42" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="D42" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>12-13</t>
+          <t>22-23</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>5.1</v>
+      </c>
+      <c r="G42" t="n">
+        <v>5.1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="C43" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D43" t="n">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>11-12</t>
+          <t>23-24</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="G43" t="n">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="44"/>
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>41</v>
+      </c>
+      <c r="B44" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>23-24</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G44" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>1.56</v>
       </c>
       <c r="C45" t="n">
         <v>0.3</v>
       </c>
       <c r="D45" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>12-13</t>
+          <t>24-25</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>3</v>
+        <v>5.7</v>
+      </c>
+      <c r="G45" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>43</v>
+      </c>
+      <c r="B46" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>24-26</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="G46" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>44</v>
+      </c>
+      <c r="B47" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="G47" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>45</v>
+      </c>
+      <c r="B48" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>25-27</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>6</v>
+      </c>
+      <c r="G48" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>46</v>
+      </c>
+      <c r="B49" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>26-28</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="G49" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>47</v>
+      </c>
+      <c r="B50" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="G50" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>48</v>
+      </c>
+      <c r="B51" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>28-29</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G51" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>49</v>
+      </c>
+      <c r="B52" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>28-30</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G52" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>50</v>
+      </c>
+      <c r="B53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>29-30</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>7</v>
+      </c>
+      <c r="G53" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
